--- a/Documentation/Event log.xlsx
+++ b/Documentation/Event log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hr\Documents\01_Low tech to the people\01_Fizzy-ball\Hardware\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC69EA7E-2AD8-4A37-BACC-DDCA85079BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46688F3B-7268-4232-9C89-A7431EC7C182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="76">
   <si>
     <t>PCB</t>
   </si>
@@ -176,9 +176,6 @@
   </si>
   <si>
     <t>TPU95A Black</t>
-  </si>
-  <si>
-    <t>old hooked one</t>
   </si>
   <si>
     <t>old</t>
@@ -215,6 +212,54 @@
 Broken motor connector on the pcb
 Students fixed it by adding wires and soldering them to the PCB at other points
 Taken out of the black shell and used the bearings for setup 3</t>
+  </si>
+  <si>
+    <t>rebuild new version for soccerball design</t>
+  </si>
+  <si>
+    <t>23 mm</t>
+  </si>
+  <si>
+    <t>polymaker TPU 90A</t>
+  </si>
+  <si>
+    <t>old one through the shell</t>
+  </si>
+  <si>
+    <t>printed in 2 parts</t>
+  </si>
+  <si>
+    <t>motor-axis connection got loose. Locktide or instant glue was not working properly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">took apart the drivetrain. Only one 4mm and 3mm bearing left and no fixed axis </t>
+  </si>
+  <si>
+    <t>replaced the drivetrain in the yellow ball. Also took the bumper from the setup 1 and the extra brass weights.</t>
+  </si>
+  <si>
+    <t>Used by BEP group for classification</t>
+  </si>
+  <si>
+    <t>months may through june</t>
+  </si>
+  <si>
+    <t>Added a washer to the battery, for better clamping force</t>
+  </si>
+  <si>
+    <t>Teal</t>
+  </si>
+  <si>
+    <t>Lend version to bachelor student Twente, added a washer, changed the o-ring</t>
+  </si>
+  <si>
+    <t>22 mm?</t>
+  </si>
+  <si>
+    <t>Used By the BEP group to test and read out IMU data</t>
+  </si>
+  <si>
+    <t>may + june</t>
   </si>
 </sst>
 </file>
@@ -562,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -770,7 +815,7 @@
         <v>46064</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -778,11 +823,32 @@
         <v>46065</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B14" s="6"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="B14" s="5">
+        <v>46114</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="B15" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -798,10 +864,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD0F91A-F783-4752-993A-8BA625570F2E}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" customWidth="1"/>
     <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -951,13 +1017,13 @@
         <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7" t="s">
         <v>6</v>
@@ -972,19 +1038,19 @@
         <v>45</v>
       </c>
       <c r="K7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" t="s">
         <v>52</v>
       </c>
-      <c r="L7" t="s">
-        <v>55</v>
-      </c>
-      <c r="M7" t="s">
-        <v>52</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>53</v>
-      </c>
-      <c r="O7" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
@@ -998,7 +1064,7 @@
     <row r="9" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
       <c r="C9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
@@ -1006,7 +1072,23 @@
         <v>46065</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="B11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>46144</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1023,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953EE5A4-2208-48A0-821E-5376883CB974}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -1036,9 +1118,9 @@
     <col min="8" max="8" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.81640625" customWidth="1"/>
+    <col min="13" max="13" width="17.1796875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.90625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.453125" bestFit="1" customWidth="1"/>
@@ -1217,24 +1299,64 @@
         <v>48</v>
       </c>
       <c r="L8" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="M8" t="s">
         <v>48</v>
       </c>
       <c r="N8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O8" t="s">
         <v>20</v>
       </c>
       <c r="P8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B10" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" t="s">
+        <v>62</v>
+      </c>
+      <c r="N10" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10" t="s">
+        <v>71</v>
+      </c>
+      <c r="P10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="2">
+        <v>46153</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1251,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C4CA03-0F3A-4744-BE3E-756773796717}">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
@@ -1263,12 +1385,12 @@
     <col min="8" max="8" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.7265625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.7265625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="40" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -1363,7 +1485,7 @@
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
@@ -1414,7 +1536,33 @@
         <v>46065</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="5">
+        <v>46114</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1426,5 +1574,6 @@
     <mergeCell ref="M1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>